--- a/product_upload/packages/39/file.xlsx
+++ b/product_upload/packages/39/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>NOYADA 25MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-D68F7E6D0C6C</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>CIALIS 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-88EE42809098</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1212,6 +1227,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ONDANSETRON MEDIS 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-345CC05A0F80</t>
         </is>
       </c>
@@ -1235,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1406,6 +1426,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>NEO-MERCAZOLE 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-A40929430BC5</t>
         </is>
       </c>
@@ -1429,7 +1454,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1592,6 +1617,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>PATANOL 0.1% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-C1A81FE3345B</t>
         </is>
       </c>
@@ -1615,7 +1645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1786,6 +1816,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>PATADAY 0.2% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-031C6B9C159F</t>
         </is>
       </c>
@@ -1809,7 +1844,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1968,6 +2003,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>NOYADA 5MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-7A11EE3504D0</t>
         </is>
       </c>
@@ -1991,7 +2031,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2162,6 +2202,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CIALIS 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-E9831A13CE76</t>
         </is>
       </c>
@@ -2185,7 +2230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2358,6 +2403,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>SILOMES 400 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-657FE7BFAA65</t>
         </is>
       </c>
@@ -2381,7 +2431,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FLOXMED 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-693729EF0C5E</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2744,6 +2799,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>EVISTA 60 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-5BF7071FF7D8</t>
         </is>
       </c>
@@ -2767,7 +2827,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2934,6 +2994,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>AROX 0.5%  EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-38832C3652ED</t>
         </is>
       </c>
@@ -2957,7 +3022,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3120,6 +3185,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>BEPANTHEN PLUS CREAM</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-BA95F25903BD</t>
         </is>
       </c>
@@ -3143,7 +3213,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3298,6 +3368,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>AZELASTIN-COMOD 0.5 mg/ml EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-4441C7352620</t>
         </is>
       </c>
@@ -3321,7 +3396,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3492,6 +3567,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>LAXATROL 50 MG/8.60 MG FILM COATED TABLET (100S)</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-05B415201216</t>
         </is>
       </c>
@@ -3515,7 +3595,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3674,6 +3754,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>TORICOX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-F2EAA76AA660</t>
         </is>
       </c>
@@ -3697,7 +3782,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3864,6 +3949,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>SUMAREX 50 MG F.C.TABLET (2S)</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-91E47B3A37D5</t>
         </is>
       </c>
@@ -3887,7 +3977,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4068,6 +4158,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CYMBALTA 60MG HARD GASTRO-RESISTANT CAP</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-DB6131446B01</t>
         </is>
       </c>
@@ -4091,7 +4186,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4250,6 +4345,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>BETOLINA 5MG/ML INJECTION</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-D7BE879EC994</t>
         </is>
       </c>
@@ -4273,7 +4373,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4444,6 +4544,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SUMAREX 50 MG F.C.TABLET (6S)</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-A96E16C3FB1A</t>
         </is>
       </c>
@@ -4467,7 +4572,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4634,6 +4739,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>SUMAREX 100 MG F.C.TABLET (2S)</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-8B428A7EB3B0</t>
         </is>
       </c>
@@ -4657,7 +4767,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4824,6 +4934,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>SUMAREX 100 MG F.C.TABLET (6S)</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-B355A0430830</t>
         </is>
       </c>
@@ -4847,7 +4962,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5010,6 +5125,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>TORICOX 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B8CEAD6B1F59</t>
         </is>
       </c>
@@ -5033,7 +5153,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5192,6 +5312,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>TORICOX 90 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-0BF6C4BED8CB</t>
         </is>
       </c>
@@ -5215,7 +5340,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5374,6 +5499,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>HENASEN 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-AC95D5C7BBC5</t>
         </is>
       </c>
@@ -5397,7 +5527,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5560,6 +5690,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>SECLODYN 1% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-ABC7F5687D04</t>
         </is>
       </c>
@@ -5583,7 +5718,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5738,6 +5873,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-65EF63A7A0BC</t>
         </is>
       </c>
@@ -5761,7 +5901,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5924,6 +6064,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>OLSAR 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-DE266599CD32</t>
         </is>
       </c>
@@ -5947,7 +6092,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6118,6 +6263,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>OLSAR 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-A114C475E0A2</t>
         </is>
       </c>
@@ -6141,7 +6291,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6308,6 +6458,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ALEVIO 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-10E08C124092</t>
         </is>
       </c>
@@ -6331,7 +6486,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6498,6 +6653,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>ALEVIO 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-F64853F68587</t>
         </is>
       </c>
@@ -6521,7 +6681,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6692,6 +6852,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>LICAN 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-6C961D91A3F6</t>
         </is>
       </c>
@@ -6715,7 +6880,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6882,6 +7047,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>TAZMERON 15MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-E22882958CE1</t>
         </is>
       </c>
@@ -6905,7 +7075,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7068,6 +7238,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>TAZMERON 30MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-B20C2CB2E6D6</t>
         </is>
       </c>
@@ -7091,7 +7266,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7250,6 +7425,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>TAZMERON 45MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-132D7AA874AF</t>
         </is>
       </c>
@@ -7273,7 +7453,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7436,6 +7616,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-F598CADEB58A</t>
         </is>
       </c>
@@ -7459,7 +7644,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7622,6 +7807,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-58C65C7473A8</t>
         </is>
       </c>
@@ -7645,7 +7835,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7808,6 +7998,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-07F46E0BF37D</t>
         </is>
       </c>
@@ -7831,7 +8026,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7990,6 +8185,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>NAUSIDOM 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-86D704E0748B</t>
         </is>
       </c>
@@ -8013,7 +8213,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8176,6 +8376,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ODECON 150 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-8F31A242998C</t>
         </is>
       </c>
@@ -8199,7 +8404,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8370,6 +8575,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ADRENALINE 0.1MG/ML INJECTION</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-66E51D8CC1B3</t>
         </is>
       </c>
@@ -8393,7 +8603,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8560,6 +8770,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>DESCOVY 200MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-64AE94750064</t>
         </is>
       </c>
@@ -8583,7 +8798,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8754,6 +8969,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>RAFOL 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-762896D665D0</t>
         </is>
       </c>
@@ -8777,7 +8997,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8942,6 +9162,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>DIOZAD</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-1716894695B6</t>
         </is>
       </c>
@@ -8965,7 +9190,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9128,6 +9353,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ALZAMED 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-F938A8A32102</t>
         </is>
       </c>
@@ -9151,7 +9381,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9314,6 +9544,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>VIZOL 0.21% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-299A2F89513A</t>
         </is>
       </c>
@@ -9337,7 +9572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9508,6 +9743,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ISONIAZID 300MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-90D24C2ED2D0</t>
         </is>
       </c>
@@ -9531,7 +9771,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9694,6 +9934,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>LATUDA 80 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-20F3FF7907A6</t>
         </is>
       </c>
@@ -9717,7 +9962,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9880,6 +10125,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ROVASTA</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-9123007B024C</t>
         </is>
       </c>
@@ -9903,7 +10153,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10062,6 +10312,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>TORLEN 20 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-54A73FCC2A67</t>
         </is>
       </c>
@@ -10085,7 +10340,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10240,6 +10495,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>CYBELLE FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-D1BD9F18F6D5</t>
         </is>
       </c>
@@ -10263,7 +10523,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10436,6 +10696,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>APROVASC 150MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-9726BC457373</t>
         </is>
       </c>
@@ -10459,7 +10724,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10618,6 +10883,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>MOMATE NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-02F2CEF82AAA</t>
         </is>
       </c>
@@ -10641,7 +10911,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10804,6 +11074,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-DB0466FE9102</t>
         </is>
       </c>
@@ -10827,7 +11102,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11002,6 +11277,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>PROZAC 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-B65ACB119F0B</t>
         </is>
       </c>
@@ -11025,7 +11305,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11196,6 +11476,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>NEUROBION tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-333B23616238</t>
         </is>
       </c>
@@ -11219,7 +11504,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11382,6 +11667,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>ACCEPT 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-3C28BD8BA160</t>
         </is>
       </c>
@@ -11405,7 +11695,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11572,6 +11862,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>D-Seul 5000 I.U SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-3F26E417FA4A</t>
         </is>
       </c>
@@ -11595,7 +11890,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11762,6 +12057,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>SABRIL 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-23573F65D22B</t>
         </is>
       </c>
@@ -11785,7 +12085,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11950,6 +12250,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>D-Seul 2000 I.U SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-2DBEFF64F09E</t>
         </is>
       </c>
@@ -11973,7 +12278,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12144,6 +12449,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DEPAKINE CHRONO 500MG TABS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-FC06A0F620D2</t>
         </is>
       </c>
@@ -12167,7 +12477,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12342,6 +12652,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Ozempic</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-69CFA5AA9B84</t>
         </is>
       </c>
@@ -12365,7 +12680,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12544,6 +12859,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Ozempic</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-C4769A5CC2D1</t>
         </is>
       </c>
@@ -12567,7 +12887,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12742,6 +13062,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Ozempic</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-A6381614E6B8</t>
         </is>
       </c>
@@ -12765,7 +13090,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12930,6 +13255,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>D-Seul 2000 I.U ORAL SOLUTION DROPS</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-9C8D026560B5</t>
         </is>
       </c>
@@ -12953,7 +13283,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13128,6 +13458,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>B COR 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-7DC22B241FB4</t>
         </is>
       </c>
@@ -13151,7 +13486,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13322,6 +13657,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>DEVARIN 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-A32C79E56DAC</t>
         </is>
       </c>
@@ -13345,7 +13685,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13510,6 +13850,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>D-Seul 10000 SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-9A36B6E3E435</t>
         </is>
       </c>
@@ -13533,7 +13878,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13706,6 +14051,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>CLEXANE 60MG\0.6ML PREFILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-B31BEDDB4E4B</t>
         </is>
       </c>
@@ -13729,7 +14079,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13896,6 +14246,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>CARDURA 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-7B7C851F9A3A</t>
         </is>
       </c>
@@ -13919,7 +14274,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14078,6 +14433,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DEVARIN 10 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-14BB6BF1CCC7</t>
         </is>
       </c>
@@ -14101,7 +14461,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14266,6 +14626,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>D-Seul 50000 SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-63F2030B4C2B</t>
         </is>
       </c>
@@ -14289,7 +14654,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14450,6 +14815,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CRESEMBA 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-DF3F83720171</t>
         </is>
       </c>
@@ -14473,7 +14843,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14644,6 +15014,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>GASTROZOLE PLUS 40/1100 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-D82EA783395C</t>
         </is>
       </c>
@@ -14667,7 +15042,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14836,6 +15211,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>SCLERA 120 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-1E791F6AC7F0</t>
         </is>
       </c>
@@ -14859,7 +15239,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15036,6 +15416,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CLEXANE 20MG\0.2ML PREFILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-9EFC82B1F54A</t>
         </is>
       </c>
@@ -15059,7 +15444,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15218,6 +15603,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>ESOMA 40 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-23860819C920</t>
         </is>
       </c>
@@ -15241,7 +15631,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15404,6 +15794,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>ESOMA 40 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-874E1E070DCD</t>
         </is>
       </c>
@@ -15427,7 +15822,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15594,6 +15989,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>CARDURA 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-09C95E3E4F37</t>
         </is>
       </c>
@@ -15617,7 +16017,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15776,6 +16176,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ESOMA 20 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-F2B894ADE636</t>
         </is>
       </c>
@@ -15799,7 +16204,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15962,6 +16367,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ESOMA 20 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-055FBB97607A</t>
         </is>
       </c>
@@ -15985,7 +16395,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16144,6 +16554,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>CELECT 100 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-4DAF8F627236</t>
         </is>
       </c>
@@ -16167,7 +16582,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16338,6 +16753,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>GASTROZOLE PLUS 20 MG/1100 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-94AB14E9FA04</t>
         </is>
       </c>
@@ -16361,7 +16781,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16528,6 +16948,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>CELECT 200 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-A22D4277D082</t>
         </is>
       </c>
@@ -16551,7 +16976,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16714,6 +17139,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>GLACERA PLUS 15MG/500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-51BAF69F015E</t>
         </is>
       </c>
@@ -16737,7 +17167,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16900,6 +17330,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>DOXENDA 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-69780EC1E8EB</t>
         </is>
       </c>
@@ -16923,7 +17358,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17078,6 +17513,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-47277AFE1F4A</t>
         </is>
       </c>
@@ -17101,7 +17541,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17272,6 +17712,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>GLACERA PLUS 15MG/850MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-AE9E9C23526B</t>
         </is>
       </c>
@@ -17295,7 +17740,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17454,6 +17899,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>DOXENDA 30 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-5B37C5EE507C</t>
         </is>
       </c>
@@ -17477,7 +17927,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17636,6 +18086,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>LEVOBAT 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-544D971C69C4</t>
         </is>
       </c>
@@ -17659,7 +18114,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17814,6 +18269,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>TEDO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-C941A04254D8</t>
         </is>
       </c>
@@ -17837,7 +18297,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18010,6 +18470,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>SCLERA 240 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-6C9DD59AB8D2</t>
         </is>
       </c>
@@ -18033,7 +18498,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18204,6 +18669,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CORTIMENT MMX 9 MG PROLONGED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-1D84B4D6A52B</t>
         </is>
       </c>
@@ -18227,7 +18697,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18386,6 +18856,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-A6FBD0B24069</t>
         </is>
       </c>
@@ -18409,7 +18884,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18580,6 +19055,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>DIVINUS 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-4B9D17B7533A</t>
         </is>
       </c>
@@ -18603,7 +19083,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18766,6 +19246,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>EZEACT PLUS 40MG/12.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-5584CF871B2C</t>
         </is>
       </c>
@@ -18789,7 +19274,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18952,6 +19437,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>DIVINUS 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-5E3B05575065</t>
         </is>
       </c>
@@ -18975,7 +19465,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19140,6 +19630,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>VIPDOMET 12.5 mg/1000 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-B93C7C2E6CEE</t>
         </is>
       </c>
@@ -19163,7 +19658,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19326,6 +19821,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>BELARA 0.03MG/2MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-49689267179C</t>
         </is>
       </c>
@@ -19349,7 +19849,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19509,6 +20009,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>VIPDOMET 12.5 mg/500 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-CC94F0DAF7F8</t>
         </is>
@@ -19525,7 +20030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19571,100 +20076,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19696,7 +20206,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19711,92 +20221,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-49326</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>401.36</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>341</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19828,7 +20343,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19843,92 +20358,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-46505</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>225.77</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>342</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19960,7 +20480,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19975,92 +20495,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-47644</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>90.67</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>343</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20092,7 +20617,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20107,92 +20632,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-87266</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>438.42</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>344</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20224,7 +20754,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20239,92 +20769,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-95840</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>492.87</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>345</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20356,7 +20891,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20371,92 +20906,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-60938</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>199.02</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>346</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20488,7 +21028,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20503,92 +21043,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-88255</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>396.71</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>347</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20620,7 +21165,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20635,92 +21180,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-57840</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>446.33</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>348</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20752,7 +21302,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20767,92 +21317,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-20951</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>203.27</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>349</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20884,7 +21439,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20899,92 +21454,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-77754</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>222.16</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>350</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21016,7 +21576,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21031,92 +21591,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-18568</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>282.01</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>351</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21133,7 +21698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21239,6 +21804,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21274,7 +21849,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21339,6 +21914,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-53D3228BA7FA</t>
         </is>
@@ -21375,7 +21960,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21440,6 +22025,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-BBA6B966163D</t>
         </is>
@@ -21476,7 +22071,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21541,6 +22136,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D8F2A9944AFD</t>
         </is>
@@ -21577,7 +22182,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21642,6 +22247,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-B4C417E24DC1</t>
         </is>
@@ -21678,7 +22293,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21743,6 +22358,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-BB5EB8C4137B</t>
         </is>
@@ -21779,7 +22404,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21844,6 +22469,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-1D6789AD1591</t>
         </is>
@@ -21880,7 +22515,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21945,6 +22580,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-BB90B4872CEA</t>
         </is>
@@ -21981,7 +22626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22046,6 +22691,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-3E51F2B106D6</t>
         </is>
@@ -22082,7 +22737,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22147,6 +22802,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-64F0F32DD62F</t>
         </is>
@@ -22183,7 +22848,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22248,6 +22913,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-33F64DDDEACE</t>
         </is>
@@ -22284,7 +22959,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22349,6 +23024,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-21EE6BEA6EF9</t>
         </is>
@@ -22385,7 +23070,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22450,6 +23135,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F3D50337D67A</t>
         </is>
@@ -22486,7 +23181,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22551,6 +23246,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-7E930D3EF483</t>
         </is>
@@ -22587,7 +23292,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22652,6 +23357,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-341E71C53D63</t>
         </is>
@@ -22688,7 +23403,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22753,6 +23468,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-498B11CEB2DE</t>
         </is>
@@ -22789,7 +23514,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22854,6 +23579,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-556A585F18AC</t>
         </is>
@@ -22890,7 +23625,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22955,6 +23690,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-EB8FAAD0533C</t>
         </is>
@@ -22991,7 +23736,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23056,6 +23801,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-22521B5E45C7</t>
         </is>
@@ -23092,7 +23847,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23157,6 +23912,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-B112A42F9B1A</t>
         </is>
@@ -23193,7 +23958,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23258,6 +24023,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-E646662F89BC</t>
         </is>

--- a/product_upload/packages/39/file.xlsx
+++ b/product_upload/packages/39/file.xlsx
@@ -686,8 +686,16 @@
           <t>3671733539-077-705213991852</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOYADA 25MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NOYADA 25MG/5ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1072,8 +1080,16 @@
           <t>0331233594-394-654583427694</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ONDANSETRON MEDIS 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ONDANSETRON MEDIS 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1852,8 +1868,16 @@
           <t>4554687807-367-645778301172</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOYADA 5MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NOYADA 5MG/5ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2439,8 +2463,16 @@
           <t>4776599200-964-542665215976</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXMED 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FLOXMED 500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -3030,8 +3062,16 @@
           <t>0225198985-297-248543354730</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEPANTHEN PLUS CREAM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BEPANTHEN PLUS CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3221,8 +3261,16 @@
           <t>4517530470-946-949347428020</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZELASTIN-COMOD 0.5 mg/ml EYE DROP</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AZELASTIN-COMOD 0.5 mg/ml EYE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3603,8 +3651,16 @@
           <t>9663937444-903-382632503056</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORICOX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TORICOX 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4194,8 +4250,16 @@
           <t>8915437337-438-044521132174</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETOLINA 5MG/ML INJECTION</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BETOLINA 5MG/ML INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4970,8 +5034,16 @@
           <t>4069429406-819-846566189959</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORICOX 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TORICOX 60 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5161,8 +5233,16 @@
           <t>5572750694-960-782266320950</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORICOX 90 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TORICOX 90 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5348,8 +5428,16 @@
           <t>6599148879-964-993935113368</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HENASEN 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>HENASEN 500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5535,8 +5623,16 @@
           <t>1862602630-003-525906992049</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SECLODYN 1% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SECLODYN 1% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5726,8 +5822,16 @@
           <t>5008315256-205-295372982885</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -7274,8 +7378,16 @@
           <t>0375862976-453-096735609546</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAZMERON 45MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TAZMERON 45MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7461,8 +7573,16 @@
           <t>9783988480-182-998208798355</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7652,8 +7772,16 @@
           <t>7868410529-487-907564178511</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AXE BRAND UNIVERSAL OIL detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7843,8 +7971,16 @@
           <t>8728979557-446-984289431773</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ANGINET</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CO-ANGINET detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8034,8 +8170,16 @@
           <t>2116719967-964-472858098107</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NAUSIDOM 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NAUSIDOM 10 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8221,8 +8365,16 @@
           <t>9738025791-032-425011727544</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ODECON 150 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ODECON 150 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8611,8 +8763,16 @@
           <t>5910730600-392-397622807127</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESCOVY 200MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DESCOVY 200MG/10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -9005,8 +9165,16 @@
           <t>1197930897-161-886182830746</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOZAD</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DIOZAD detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -9198,8 +9366,16 @@
           <t>0651312131-870-078135425194</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALZAMED 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ALZAMED 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9779,8 +9955,16 @@
           <t>9244965860-981-359781247559</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LATUDA 80 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>LATUDA 80 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9970,8 +10154,16 @@
           <t>2390287894-107-608715378078</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROVASTA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ROVASTA detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10161,8 +10353,16 @@
           <t>6335179909-292-070275561235</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TORLEN 20 MG FILM-COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TORLEN 20 MG FILM-COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10348,8 +10548,16 @@
           <t>1808046512-481-322075337411</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYBELLE FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CYBELLE FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10732,8 +10940,16 @@
           <t>8889070762-737-372823588365</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOMATE NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>MOMATE NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10919,8 +11135,16 @@
           <t>7779604520-747-767535581222</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11512,8 +11736,16 @@
           <t>9498648171-903-744581310892</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACCEPT 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACCEPT 250MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -12093,8 +12325,16 @@
           <t>1854429282-721-018371264802</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-Seul 2000 I.U SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D-Seul 2000 I.U SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -13098,8 +13338,16 @@
           <t>0966192605-823-285103399850</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-Seul 2000 I.U ORAL SOLUTION DROPS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D-Seul 2000 I.U ORAL SOLUTION DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -14282,8 +14530,16 @@
           <t>1148695412-162-317353017905</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEVARIN 10 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DEVARIN 10 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14469,8 +14725,16 @@
           <t>2538128977-827-918664641773</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-Seul 50000 SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D-Seul 50000 SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -14662,8 +14926,16 @@
           <t>6602821011-298-405254654340</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CRESEMBA 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CRESEMBA 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -15452,8 +15724,16 @@
           <t>2086926044-871-212957721830</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMA 40 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ESOMA 40 MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15639,8 +15919,16 @@
           <t>9201455303-040-718184915951</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMA 40 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ESOMA 40 MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15830,8 +16118,16 @@
           <t>2513391938-957-159771047781</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDURA 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CARDURA 2 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16025,8 +16321,16 @@
           <t>3708825773-760-460307908956</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMA 20 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ESOMA 20 MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16212,8 +16516,16 @@
           <t>4917128040-441-617543871410</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMA 20 MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ESOMA 20 MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16403,8 +16715,16 @@
           <t>5264806336-039-816853611419</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELECT 100 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CELECT 100 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16984,8 +17304,16 @@
           <t>9110749071-912-234088241571</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLACERA PLUS 15MG/500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GLACERA PLUS 15MG/500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17175,8 +17503,16 @@
           <t>6172703740-025-081280078311</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DOXENDA 60 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DOXENDA 60 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17366,8 +17702,16 @@
           <t>5337698363-941-362694397485</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COXICEL 200 MG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>COXICEL 200 MG HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17748,8 +18092,16 @@
           <t>3039730282-722-179566559311</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DOXENDA 30 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DOXENDA 30 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17935,8 +18287,16 @@
           <t>7012645538-669-034636677924</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOBAT 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LEVOBAT 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18122,8 +18482,16 @@
           <t>7648083630-014-523647706606</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEDO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TEDO 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18705,8 +19073,16 @@
           <t>3368348661-841-353769184177</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COXICEL 200 MG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>COXICEL 200 MG HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19091,8 +19467,16 @@
           <t>5107760337-674-615588095117</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT PLUS 40MG/12.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>EZEACT PLUS 40MG/12.5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19857,8 +20241,16 @@
           <t>5073289198-287-311279354844</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIPDOMET 12.5 mg/500 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>VIPDOMET 12.5 mg/500 mg TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>

--- a/product_upload/packages/39/file.xlsx
+++ b/product_upload/packages/39/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22090,7 +22090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22171,40 +22171,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22284,38 +22289,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>101.25</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-53D3228BA7FA</t>
         </is>
@@ -22395,38 +22405,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>493.01</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-BBA6B966163D</t>
         </is>
@@ -22506,38 +22521,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>221.39</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D8F2A9944AFD</t>
         </is>
@@ -22617,38 +22637,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>232.82</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-B4C417E24DC1</t>
         </is>
@@ -22728,38 +22753,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>492.55</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-BB5EB8C4137B</t>
         </is>
@@ -22839,38 +22869,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>429.99</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-1D6789AD1591</t>
         </is>
@@ -22950,38 +22985,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>344.38</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-BB90B4872CEA</t>
         </is>
@@ -23061,38 +23101,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>38.52</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-3E51F2B106D6</t>
         </is>
@@ -23172,38 +23217,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>275.09</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-64F0F32DD62F</t>
         </is>
@@ -23283,38 +23333,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>189.2</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-33F64DDDEACE</t>
         </is>
@@ -23394,38 +23449,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>223.35</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-21EE6BEA6EF9</t>
         </is>
@@ -23505,38 +23565,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>342.7</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F3D50337D67A</t>
         </is>
@@ -23616,38 +23681,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>133.52</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-7E930D3EF483</t>
         </is>
@@ -23727,38 +23797,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>112.6</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-341E71C53D63</t>
         </is>
@@ -23838,38 +23913,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>281.49</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-498B11CEB2DE</t>
         </is>
@@ -23949,38 +24029,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>203.55</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-556A585F18AC</t>
         </is>
@@ -24060,38 +24145,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>492.31</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-EB8FAAD0533C</t>
         </is>
@@ -24171,38 +24261,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>176</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-22521B5E45C7</t>
         </is>
@@ -24282,38 +24377,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>190.19</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-B112A42F9B1A</t>
         </is>
@@ -24393,38 +24493,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>381.58</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-E646662F89BC</t>
         </is>
